--- a/Data/FlightPlan/FPL_01SEP26.xlsx
+++ b/Data/FlightPlan/FPL_01SEP26.xlsx
@@ -290,15 +290,558 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>VN-A546</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
     <t>16:45</t>
   </si>
   <si>
     <t>17:35</t>
   </si>
   <si>
-    <t>VII</t>
-  </si>
-  <si>
     <t>20:20</t>
   </si>
   <si>
@@ -308,546 +851,6 @@
     <t>22:40</t>
   </si>
   <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A546</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -959,9 +962,6 @@
     <t>06:55</t>
   </si>
   <si>
-    <t>09:05</t>
-  </si>
-  <si>
     <t>CMB</t>
   </si>
   <si>
@@ -1169,6 +1169,9 @@
     <t>04:05</t>
   </si>
   <si>
+    <t>07:22</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1235,7 +1238,7 @@
     <t>Total Record(s): 432</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 31, 2026 21:14</t>
+    <t xml:space="preserve">Generated on  Sep 01, 2026 02:29</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2854,7 +2857,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
@@ -2870,13 +2873,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2887,7 +2890,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
@@ -2900,16 +2903,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2920,7 +2923,7 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>1216</v>
+        <v>154</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
@@ -2936,13 +2939,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2953,7 +2956,7 @@
         <v>13</v>
       </c>
       <c r="B45" s="7">
-        <v>1217</v>
+        <v>163</v>
       </c>
       <c t="s" r="C45" s="7">
         <v>14</v>
@@ -2966,16 +2969,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3008,7 +3011,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3017,13 +3020,13 @@
         <v>75</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3041,22 +3044,22 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3074,22 +3077,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I49" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3107,22 +3110,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3155,7 +3158,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3164,10 +3167,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J52" s="7">
         <v>84</v>
@@ -3188,13 +3191,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>25</v>
@@ -3203,7 +3206,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3221,7 +3224,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3230,10 +3233,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>67</v>
@@ -3254,22 +3257,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3302,7 +3305,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3317,7 +3320,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3335,7 +3338,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3347,10 +3350,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3368,7 +3371,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3377,10 +3380,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>30</v>
@@ -3401,22 +3404,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3449,7 +3452,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3458,10 +3461,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>49</v>
@@ -3482,19 +3485,19 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>128</v>
@@ -3515,7 +3518,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3548,7 +3551,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3608,7 +3611,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>133</v>
@@ -3641,7 +3644,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>81</v>
@@ -3836,7 +3839,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>89</v>
@@ -3935,7 +3938,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>79</v>
@@ -4034,7 +4037,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>81</v>
@@ -4067,7 +4070,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>58</v>
@@ -4103,7 +4106,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4115,10 +4118,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4136,7 +4139,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4151,7 +4154,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4169,7 +4172,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4184,7 +4187,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4202,7 +4205,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4214,10 +4217,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I87" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J87" s="7">
         <v>151</v>
-      </c>
-      <c t="s" r="J87" s="7">
-        <v>152</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4247,10 +4250,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I88" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J88" s="7">
         <v>153</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>154</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4268,7 +4271,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4280,10 +4283,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I89" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J89" s="7">
         <v>155</v>
-      </c>
-      <c t="s" r="J89" s="7">
-        <v>156</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4316,7 +4319,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4328,10 +4331,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I91" s="7">
+        <v>157</v>
+      </c>
+      <c t="s" r="J91" s="7">
         <v>158</v>
-      </c>
-      <c t="s" r="J91" s="7">
-        <v>159</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4349,7 +4352,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4358,13 +4361,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I92" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="J92" s="7">
         <v>160</v>
-      </c>
-      <c t="s" r="J92" s="7">
-        <v>161</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4382,22 +4385,22 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I93" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="J93" s="7">
         <v>162</v>
-      </c>
-      <c t="s" r="J93" s="7">
-        <v>163</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4415,7 +4418,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4430,7 +4433,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4448,7 +4451,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4481,7 +4484,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4490,13 +4493,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I96" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4514,22 +4517,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I97" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J97" s="7">
         <v>166</v>
-      </c>
-      <c t="s" r="J97" s="7">
-        <v>167</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4547,7 +4550,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4595,7 +4598,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4607,10 +4610,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4628,7 +4631,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4637,13 +4640,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H101" s="8">
+        <v>169</v>
+      </c>
+      <c t="s" r="I101" s="7">
         <v>170</v>
       </c>
-      <c t="s" r="I101" s="7">
+      <c t="s" r="J101" s="7">
         <v>171</v>
-      </c>
-      <c t="s" r="J101" s="7">
-        <v>172</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4661,19 +4664,19 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>24</v>
@@ -4694,7 +4697,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4706,10 +4709,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I103" s="7">
+        <v>172</v>
+      </c>
+      <c t="s" r="J103" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="J103" s="7">
-        <v>174</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4742,7 +4745,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4754,10 +4757,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I105" s="7">
+        <v>175</v>
+      </c>
+      <c t="s" r="J105" s="7">
         <v>176</v>
-      </c>
-      <c t="s" r="J105" s="7">
-        <v>177</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4775,7 +4778,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4790,7 +4793,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4808,7 +4811,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4820,10 +4823,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I107" s="7">
+        <v>178</v>
+      </c>
+      <c t="s" r="J107" s="7">
         <v>179</v>
-      </c>
-      <c t="s" r="J107" s="7">
-        <v>180</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4841,7 +4844,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4850,10 +4853,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H108" s="8">
+        <v>180</v>
+      </c>
+      <c t="s" r="I108" s="7">
         <v>181</v>
-      </c>
-      <c t="s" r="I108" s="7">
-        <v>182</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>145</v>
@@ -4874,19 +4877,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>54</v>
@@ -4907,7 +4910,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4916,13 +4919,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="I110" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4940,19 +4943,19 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>73</v>
@@ -4988,7 +4991,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4997,7 +5000,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>87</v>
@@ -5021,19 +5024,19 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
+        <v>184</v>
+      </c>
+      <c r="F114" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G114" s="8">
+        <v>185</v>
+      </c>
+      <c t="s" r="H114" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I114" s="7">
         <v>186</v>
-      </c>
-      <c r="F114" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G114" s="8">
-        <v>187</v>
-      </c>
-      <c t="s" r="H114" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I114" s="7">
-        <v>188</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>18</v>
@@ -5054,7 +5057,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5087,7 +5090,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5099,7 +5102,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>21</v>
@@ -5120,7 +5123,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5132,10 +5135,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5153,7 +5156,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5165,7 +5168,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>137</v>
@@ -5186,7 +5189,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5198,10 +5201,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5230,11 +5233,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C121" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5243,13 +5246,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5263,23 +5266,23 @@
         <v>8521</v>
       </c>
       <c t="s" r="C122" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>23</v>
@@ -5300,7 +5303,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5312,10 +5315,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5348,7 +5351,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5360,7 +5363,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>21</v>
@@ -5381,7 +5384,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5396,7 +5399,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5414,7 +5417,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5447,7 +5450,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5459,10 +5462,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5495,7 +5498,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5507,7 +5510,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>77</v>
@@ -5528,7 +5531,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5537,13 +5540,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5561,22 +5564,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5594,7 +5597,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5603,13 +5606,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
+        <v>203</v>
+      </c>
+      <c t="s" r="I133" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J133" s="7">
         <v>205</v>
-      </c>
-      <c t="s" r="I133" s="7">
-        <v>206</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>207</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5642,22 +5645,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5675,7 +5678,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5684,13 +5687,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5708,13 +5711,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>17</v>
@@ -5741,7 +5744,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5753,10 +5756,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5789,19 +5792,19 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
+        <v>212</v>
+      </c>
+      <c r="F140" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G140" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H140" s="8">
         <v>213</v>
       </c>
-      <c r="F140" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G140" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H140" s="8">
-        <v>214</v>
-      </c>
       <c t="s" r="I140" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>76</v>
@@ -5822,22 +5825,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
+        <v>212</v>
+      </c>
+      <c r="F141" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G141" s="8">
         <v>213</v>
       </c>
-      <c r="F141" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G141" s="8">
+      <c t="s" r="H141" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I141" s="7">
         <v>214</v>
       </c>
-      <c t="s" r="H141" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I141" s="7">
+      <c t="s" r="J141" s="7">
         <v>215</v>
-      </c>
-      <c t="s" r="J141" s="7">
-        <v>216</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5855,7 +5858,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5867,7 +5870,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>71</v>
@@ -5884,11 +5887,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5900,10 +5903,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5917,11 +5920,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5930,10 +5933,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
+        <v>217</v>
+      </c>
+      <c t="s" r="I144" s="7">
         <v>218</v>
-      </c>
-      <c t="s" r="I144" s="7">
-        <v>219</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>84</v>
@@ -5969,7 +5972,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5981,10 +5984,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5998,11 +6001,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C147" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6017,7 +6020,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6031,11 +6034,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C148" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6044,7 +6047,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>145</v>
@@ -6064,26 +6067,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C149" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6116,7 +6119,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6128,43 +6131,47 @@
         <v>25</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>202</v>
-      </c>
-      <c r="K151" s="7"/>
+        <v>200</v>
+      </c>
+      <c t="s" r="K151" s="7">
+        <v>225</v>
+      </c>
       <c r="L151" s="7"/>
-      <c r="M151" s="7"/>
+      <c t="s" r="M151" s="7">
+        <v>47</v>
+      </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>214</v>
+        <v>600</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
+        <v>224</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H152" s="8">
+        <v>61</v>
+      </c>
+      <c t="s" r="I152" s="7">
+        <v>79</v>
+      </c>
+      <c t="s" r="J152" s="7">
         <v>226</v>
-      </c>
-      <c r="F152" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G152" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H152" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="I152" s="7">
-        <v>127</v>
-      </c>
-      <c t="s" r="J152" s="7">
-        <v>227</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6175,26 +6182,26 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>213</v>
+        <v>601</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>228</v>
@@ -6208,14 +6215,14 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6224,13 +6231,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6241,29 +6248,29 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>229</v>
+        <v>24</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6281,7 +6288,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6293,10 +6300,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6329,7 +6336,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6341,10 +6348,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6362,7 +6369,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6374,10 +6381,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6410,7 +6417,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6419,13 +6426,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6443,19 +6450,19 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>51</v>
@@ -6476,7 +6483,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6485,13 +6492,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6509,13 +6516,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>25</v>
@@ -6524,7 +6531,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6557,7 +6564,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6590,7 +6597,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6599,13 +6606,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6623,13 +6630,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>25</v>
@@ -6638,7 +6645,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6671,7 +6678,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6683,7 +6690,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>66</v>
@@ -6704,7 +6711,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6716,7 +6723,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>53</v>
@@ -6737,7 +6744,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6746,13 +6753,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6770,22 +6777,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6803,7 +6810,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6815,10 +6822,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6836,7 +6843,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6851,7 +6858,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6884,7 +6891,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6893,13 +6900,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6917,22 +6924,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6950,7 +6957,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6965,7 +6972,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6983,7 +6990,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6998,7 +7005,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7016,7 +7023,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7028,10 +7035,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7064,7 +7071,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7076,10 +7083,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7097,7 +7104,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7109,10 +7116,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7130,7 +7137,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7139,13 +7146,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7163,19 +7170,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>49</v>
@@ -7196,7 +7203,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7205,13 +7212,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7229,19 +7236,19 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>128</v>
@@ -7262,7 +7269,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7274,7 +7281,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>26</v>
@@ -7295,7 +7302,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7307,10 +7314,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I190" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J190" s="7">
         <v>155</v>
-      </c>
-      <c t="s" r="J190" s="7">
-        <v>156</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7343,7 +7350,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7355,10 +7362,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7376,7 +7383,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7388,10 +7395,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7409,7 +7416,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7421,10 +7428,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7442,7 +7449,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7454,7 +7461,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>69</v>
@@ -7490,7 +7497,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7502,7 +7509,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>90</v>
@@ -7523,7 +7530,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7538,7 +7545,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7556,7 +7563,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7568,10 +7575,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7604,7 +7611,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7613,13 +7620,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7637,22 +7644,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7670,7 +7677,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7682,10 +7689,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7703,7 +7710,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7715,7 +7722,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>72</v>
@@ -7751,7 +7758,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7766,7 +7773,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7784,7 +7791,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7799,7 +7806,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7817,7 +7824,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7826,10 +7833,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>68</v>
@@ -7850,22 +7857,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7898,7 +7905,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7907,7 +7914,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>18</v>
@@ -7931,13 +7938,13 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>25</v>
@@ -7964,7 +7971,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7976,10 +7983,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7997,7 +8004,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8009,10 +8016,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8030,7 +8037,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8045,7 +8052,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8063,7 +8070,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8075,10 +8082,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8111,7 +8118,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8120,13 +8127,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8144,19 +8151,19 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>31</v>
@@ -8177,7 +8184,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8186,13 +8193,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8210,13 +8217,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>25</v>
@@ -8225,7 +8232,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8236,14 +8243,14 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>600</v>
+        <v>192</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8252,13 +8259,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8269,29 +8276,29 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>601</v>
+        <v>141</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>276</v>
+        <v>56</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8302,14 +8309,14 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>262</v>
+        <v>1216</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8318,13 +8325,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H224" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="I224" s="7">
         <v>277</v>
       </c>
-      <c t="s" r="I224" s="7">
+      <c t="s" r="J224" s="7">
         <v>278</v>
-      </c>
-      <c t="s" r="J224" s="7">
-        <v>80</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8335,29 +8342,29 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>263</v>
+        <v>1217</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>277</v>
+        <v>93</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>24</v>
+        <v>279</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8390,7 +8397,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8402,7 +8409,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>42</v>
@@ -8423,7 +8430,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8435,10 +8442,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8456,7 +8463,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8465,13 +8472,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8489,22 +8496,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8522,7 +8529,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8531,13 +8538,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8555,19 +8562,19 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>24</v>
@@ -8588,7 +8595,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8597,13 +8604,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8621,22 +8628,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8669,7 +8676,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8678,13 +8685,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8702,19 +8709,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>142</v>
@@ -8735,7 +8742,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8744,13 +8751,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8768,13 +8775,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>25</v>
@@ -8801,7 +8808,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8810,13 +8817,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8834,13 +8841,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>25</v>
@@ -8849,7 +8856,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8882,7 +8889,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8891,13 +8898,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8915,22 +8922,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8948,22 +8955,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8981,22 +8988,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9029,7 +9036,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9041,10 +9048,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9062,7 +9069,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9071,7 +9078,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>76</v>
@@ -9095,13 +9102,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>44</v>
@@ -9128,7 +9135,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9140,7 +9147,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>68</v>
@@ -9161,7 +9168,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9173,10 +9180,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9194,7 +9201,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9206,10 +9213,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9242,7 +9249,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9254,7 +9261,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>140</v>
@@ -9275,7 +9282,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9287,10 +9294,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9308,7 +9315,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9323,7 +9330,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9341,7 +9348,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9350,13 +9357,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9374,19 +9381,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>44</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>53</v>
@@ -9407,7 +9414,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9419,7 +9426,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>24</v>
@@ -9440,7 +9447,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9449,13 +9456,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9473,22 +9480,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9521,7 +9528,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9533,7 +9540,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>77</v>
@@ -9554,7 +9561,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9569,7 +9576,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9587,7 +9594,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9596,13 +9603,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9620,22 +9627,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9668,7 +9675,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9677,13 +9684,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9701,22 +9708,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9734,7 +9741,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9743,10 +9750,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>49</v>
@@ -9767,22 +9774,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9800,7 +9807,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9809,13 +9816,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>93</v>
+        <v>275</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9833,13 +9840,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>17</v>
@@ -9848,7 +9855,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9866,7 +9873,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9878,10 +9885,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9914,7 +9921,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9926,7 +9933,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>88</v>
@@ -9947,7 +9954,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9956,13 +9963,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9980,13 +9987,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -9995,7 +10002,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10013,7 +10020,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10022,10 +10029,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>145</v>
@@ -10046,13 +10053,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
@@ -10061,7 +10068,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10079,7 +10086,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10094,7 +10101,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10112,7 +10119,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10160,7 +10167,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10172,10 +10179,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>316</v>
+        <v>225</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10193,7 +10200,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10205,10 +10212,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10226,7 +10233,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10235,7 +10242,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>79</v>
@@ -10259,19 +10266,19 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>145</v>
@@ -10292,7 +10299,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10307,7 +10314,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10325,7 +10332,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10382,7 +10389,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>131</v>
@@ -10412,16 +10419,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10448,7 +10455,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>320</v>
@@ -10478,7 +10485,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>25</v>
@@ -10487,7 +10494,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>94</v>
+        <v>276</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10514,13 +10521,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10544,7 +10551,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>25</v>
@@ -10631,10 +10638,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10667,7 +10674,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10697,10 +10704,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10742,7 +10749,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>73</v>
@@ -10772,16 +10779,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10808,13 +10815,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10838,16 +10845,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10913,7 +10920,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10940,13 +10947,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I310" s="7">
         <v>325</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10970,7 +10977,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>25</v>
@@ -11006,13 +11013,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>326</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11036,7 +11043,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>25</v>
@@ -11045,7 +11052,7 @@
         <v>327</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11087,13 +11094,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11117,16 +11124,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11150,13 +11157,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>19</v>
@@ -11183,7 +11190,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
@@ -11192,7 +11199,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11222,10 +11229,10 @@
         <v>329</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11255,7 +11262,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>330</v>
@@ -11300,13 +11307,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11330,7 +11337,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>25</v>
@@ -11339,7 +11346,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11366,10 +11373,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>332</v>
@@ -11396,13 +11403,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>330</v>
@@ -11435,7 +11442,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>57</v>
@@ -11516,10 +11523,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11546,13 +11553,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11576,16 +11583,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11633,7 +11640,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11666,7 +11673,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11693,10 +11700,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>64</v>
@@ -11723,16 +11730,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11762,7 +11769,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>133</v>
@@ -11795,10 +11802,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11828,10 +11835,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11864,7 +11871,7 @@
         <v>338</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11942,10 +11949,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11975,7 +11982,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>342</v>
@@ -12008,7 +12015,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>21</v>
@@ -12044,7 +12051,7 @@
         <v>321</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12077,7 +12084,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12125,7 +12132,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12158,7 +12165,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12185,7 +12192,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>320</v>
@@ -12215,13 +12222,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>145</v>
@@ -12251,10 +12258,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>69</v>
@@ -12281,7 +12288,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>48</v>
@@ -12335,10 +12342,10 @@
         <v>345</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12368,7 +12375,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>52</v>
@@ -12398,13 +12405,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12428,7 +12435,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>17</v>
@@ -12485,7 +12492,7 @@
         <v>348</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12512,7 +12519,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>49</v>
@@ -12542,7 +12549,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>17</v>
@@ -12551,7 +12558,7 @@
         <v>321</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12614,7 +12621,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>338</v>
@@ -12647,7 +12654,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>88</v>
@@ -12695,7 +12702,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>319</v>
@@ -12728,7 +12735,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>91</v>
@@ -12764,7 +12771,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12794,10 +12801,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12860,10 +12867,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12893,7 +12900,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>350</v>
@@ -12938,13 +12945,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12968,13 +12975,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>79</v>
@@ -13004,13 +13011,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13034,7 +13041,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
@@ -13043,7 +13050,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13073,10 +13080,10 @@
         <v>352</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13151,13 +13158,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13181,13 +13188,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>22</v>
@@ -13298,10 +13305,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>63</v>
@@ -13328,7 +13335,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>25</v>
@@ -13337,7 +13344,7 @@
         <v>359</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13364,13 +13371,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13394,7 +13401,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>25</v>
@@ -13403,7 +13410,7 @@
         <v>320</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13430,13 +13437,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13460,16 +13467,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13502,7 +13509,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13544,13 +13551,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13574,7 +13581,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>17</v>
@@ -13610,13 +13617,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13640,7 +13647,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
@@ -13649,7 +13656,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>93</v>
+        <v>275</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13676,13 +13683,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13706,7 +13713,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>17</v>
@@ -13760,10 +13767,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13790,13 +13797,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13820,13 +13827,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>54</v>
@@ -13874,10 +13881,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13907,7 +13914,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>133</v>
@@ -13940,10 +13947,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13973,10 +13980,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14018,7 +14025,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>364</v>
@@ -14048,13 +14055,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>49</v>
@@ -14084,13 +14091,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14114,13 +14121,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>68</v>
@@ -14165,10 +14172,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>91</v>
@@ -14195,16 +14202,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14231,13 +14238,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14261,16 +14268,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14297,13 +14304,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14327,16 +14334,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14384,7 +14391,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14411,13 +14418,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14441,7 +14448,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>17</v>
@@ -14450,7 +14457,7 @@
         <v>367</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>93</v>
+        <v>275</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14480,7 +14487,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>368</v>
@@ -14513,10 +14520,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14558,10 +14565,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>89</v>
@@ -14588,7 +14595,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>48</v>
@@ -14624,7 +14631,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I432" s="7">
         <v>92</v>
@@ -14654,13 +14661,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>325</v>
@@ -14690,7 +14697,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>128</v>
@@ -14720,7 +14727,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>48</v>
@@ -14729,7 +14736,7 @@
         <v>327</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14759,7 +14766,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>87</v>
@@ -14804,13 +14811,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14834,7 +14841,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>25</v>
@@ -14843,7 +14850,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14870,13 +14877,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>142</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14900,7 +14907,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>44</v>
@@ -14936,13 +14943,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>321</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14966,7 +14973,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>25</v>
@@ -15005,10 +15012,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15083,7 +15090,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I447" s="7">
         <v>62</v>
@@ -15113,16 +15120,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15149,13 +15156,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15179,16 +15186,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15251,10 +15258,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>97</v>
+        <v>278</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15296,13 +15303,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15326,16 +15333,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15359,16 +15366,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I456" s="7">
         <v>348</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15392,13 +15399,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>49</v>
@@ -15428,10 +15435,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J458" s="7">
         <v>321</v>
@@ -15458,7 +15465,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>25</v>
@@ -15467,7 +15474,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15494,13 +15501,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15524,7 +15531,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>25</v>
@@ -15575,7 +15582,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>377</v>
@@ -15605,13 +15612,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>84</v>
@@ -15641,7 +15648,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>37</v>
@@ -15671,7 +15678,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>17</v>
@@ -15707,7 +15714,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>144</v>
@@ -15737,16 +15744,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -15776,7 +15783,7 @@
         <v>355</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>371</v>
@@ -15854,10 +15861,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>45</v>
@@ -15884,13 +15891,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="J473" s="7">
         <v>89</v>
@@ -15920,10 +15927,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H474" s="8">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J474" s="7">
         <v>21</v>
@@ -15950,7 +15957,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>25</v>
@@ -15959,7 +15966,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -15986,7 +15993,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="I476" s="7">
         <v>80</v>
@@ -16016,13 +16023,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>383</v>
@@ -16067,17 +16074,19 @@
         <v>33</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I479" s="7">
         <v>385</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
-      <c r="M479" s="7"/>
+      <c t="s" r="M479" s="7">
+        <v>386</v>
+      </c>
     </row>
     <row r="480" ht="15" customHeight="1">
       <c t="s" r="A480" s="6">
@@ -16097,16 +16106,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H480" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="I480" s="7">
         <v>364</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16130,13 +16139,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G481" s="8">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="H481" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>53</v>
@@ -16163,16 +16172,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G482" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H482" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -16205,7 +16214,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
@@ -16214,13 +16223,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H484" s="8">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16238,22 +16247,22 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F485" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G485" s="8">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c t="s" r="H485" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I485" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
@@ -16271,7 +16280,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -16280,10 +16289,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H486" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>378</v>
@@ -16304,19 +16313,19 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G487" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H487" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I487" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J487" s="7">
         <v>136</v>
@@ -16337,7 +16346,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -16346,13 +16355,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H488" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I488" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -16370,13 +16379,13 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G489" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H489" s="8">
         <v>25</v>
@@ -16385,7 +16394,7 @@
         <v>332</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
@@ -16403,7 +16412,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -16415,10 +16424,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
@@ -16432,11 +16441,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C491" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
@@ -16451,7 +16460,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -16465,11 +16474,11 @@
         <v>8021</v>
       </c>
       <c t="s" r="C492" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -16481,10 +16490,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I492" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
@@ -16517,7 +16526,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F494" s="7">
         <v>320</v>
@@ -16550,7 +16559,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F495" s="7">
         <v>320</v>
@@ -16583,7 +16592,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F496" s="7">
         <v>320</v>
@@ -16595,10 +16604,10 @@
         <v>324</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -16616,7 +16625,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F497" s="7">
         <v>320</v>
@@ -16628,10 +16637,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I497" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J497" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
@@ -16649,7 +16658,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F498" s="7">
         <v>320</v>
@@ -16661,7 +16670,7 @@
         <v>352</v>
       </c>
       <c t="s" r="I498" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J498" s="7">
         <v>130</v>
@@ -16682,7 +16691,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -16694,10 +16703,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I499" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J499" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
@@ -16730,7 +16739,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F501" s="7">
         <v>330</v>
@@ -16745,7 +16754,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J501" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
@@ -16778,22 +16787,22 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F503" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G503" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H503" s="8">
         <v>61</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
@@ -16811,7 +16820,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F504" s="7">
         <v>330</v>
@@ -16820,13 +16829,13 @@
         <v>61</v>
       </c>
       <c t="s" r="H504" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I504" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J504" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
@@ -16859,7 +16868,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F506" s="7">
         <v>330</v>
@@ -16868,13 +16877,13 @@
         <v>61</v>
       </c>
       <c t="s" r="H506" s="8">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J506" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
@@ -16892,13 +16901,13 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F507" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G507" s="8">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="H507" s="8">
         <v>61</v>
@@ -16907,7 +16916,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J507" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
@@ -16940,7 +16949,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F509" s="7">
         <v>330</v>
@@ -16949,13 +16958,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H509" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I509" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J509" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
@@ -16973,19 +16982,19 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F510" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G510" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H510" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I510" s="7">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c t="s" r="J510" s="7">
         <v>377</v>
@@ -17021,7 +17030,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F512" s="7">
         <v>330</v>
@@ -17030,10 +17039,10 @@
         <v>61</v>
       </c>
       <c t="s" r="H512" s="8">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c t="s" r="I512" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J512" s="7">
         <v>330</v>
@@ -17054,22 +17063,22 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F513" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G513" s="8">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c t="s" r="H513" s="8">
         <v>61</v>
       </c>
       <c t="s" r="I513" s="7">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c t="s" r="J513" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
@@ -17102,7 +17111,7 @@
       </c>
       <c r="D515" s="7"/>
       <c t="s" r="E515" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F515" s="7">
         <v>330</v>
@@ -17111,7 +17120,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H515" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="I515" s="7">
         <v>87</v>
@@ -17135,13 +17144,13 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F516" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G516" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H516" s="8">
         <v>48</v>
@@ -17150,7 +17159,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
@@ -17183,7 +17192,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F518" s="7">
         <v>330</v>
@@ -17195,7 +17204,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I518" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="J518" s="7">
         <v>37</v>
@@ -17216,7 +17225,7 @@
       </c>
       <c r="D519" s="7"/>
       <c t="s" r="E519" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F519" s="7">
         <v>330</v>
@@ -17228,7 +17237,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I519" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J519" s="7">
         <v>77</v>
@@ -17249,7 +17258,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F520" s="7">
         <v>330</v>
@@ -17258,13 +17267,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H520" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="I520" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J520" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
@@ -17272,7 +17281,7 @@
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c t="s" r="A521" s="9">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
@@ -17292,7 +17301,7 @@
     <row r="522" ht="65.25" customHeight="1"/>
     <row r="523" ht="16.5" customHeight="1">
       <c t="s" r="A523" s="10">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B523" s="10"/>
       <c r="C523" s="10"/>
@@ -17305,7 +17314,7 @@
       <c r="J523" s="10"/>
       <c r="K523" s="10"/>
       <c t="s" r="L523" s="11">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M523" s="11"/>
       <c r="N523" s="11"/>
